--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-medicationdosage.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-medicationdosage.xlsx
@@ -1107,7 +1107,7 @@
     <t>薬が投与される手法を説明するコード化された概念。 / A coded concept describing the technique by which the medicine is administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>.doseQuantity</t>
@@ -1427,7 +1427,7 @@
   </si>
   <si>
     <t>Ratio
-RangeQuantity {SimpleQuantity}</t>
+RangeQuantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>薬剤の投与量速度</t>
